--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.15503513898092</v>
+      </c>
+      <c r="C2">
         <v>25.07684954867862</v>
-      </c>
-      <c r="C2">
-        <v>29.15503513898092</v>
       </c>
       <c r="D2">
         <v>3.987741753838824</v>
       </c>
       <c r="E2">
+        <v>18.90337733862477</v>
+      </c>
+      <c r="F2">
+        <v>64.8374363073586</v>
+      </c>
+      <c r="G2">
         <v>16.25918635401664</v>
-      </c>
-      <c r="F2">
-        <v>64.83743630735859</v>
-      </c>
-      <c r="G2">
-        <v>18.90337733862477</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>34.38134538547193</v>
+      </c>
+      <c r="C3">
         <v>34.93810178817056</v>
-      </c>
-      <c r="C3">
-        <v>34.38134538547193</v>
       </c>
       <c r="D3">
         <v>2.862204724409449</v>
       </c>
       <c r="E3">
-        <v>20.63442940038684</v>
+        <v>20.30560928433269</v>
       </c>
       <c r="F3">
         <v>59.05996131528046</v>
       </c>
       <c r="G3">
-        <v>20.30560928433269</v>
+        <v>20.63442940038684</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.23510084877248</v>
+      </c>
+      <c r="C4">
         <v>40.40339508989687</v>
-      </c>
-      <c r="C4">
-        <v>32.23510084877248</v>
       </c>
       <c r="D4">
         <v>2.475039530155862</v>
       </c>
       <c r="E4">
-        <v>23.40346796362867</v>
+        <v>18.67202368365405</v>
       </c>
       <c r="F4">
         <v>57.92450835271728</v>
       </c>
       <c r="G4">
-        <v>18.67202368365405</v>
+        <v>23.40346796362867</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.98495486459378</v>
+      </c>
+      <c r="C5">
         <v>30.37111334002006</v>
-      </c>
-      <c r="C5">
-        <v>34.98495486459378</v>
       </c>
       <c r="D5">
         <v>3.292602377807134</v>
       </c>
       <c r="E5">
-        <v>18.36709935703021</v>
+        <v>21.15734562659226</v>
       </c>
       <c r="F5">
         <v>60.47555501637753</v>
       </c>
       <c r="G5">
-        <v>21.15734562659226</v>
+        <v>18.36709935703021</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.51766806990688</v>
+      </c>
+      <c r="C6">
         <v>33.55019772930221</v>
-      </c>
-      <c r="C6">
-        <v>28.51766806990688</v>
       </c>
       <c r="D6">
         <v>2.980608365019012</v>
       </c>
       <c r="E6">
-        <v>20.70132630170412</v>
+        <v>17.59612735644851</v>
       </c>
       <c r="F6">
         <v>61.70254634184738</v>
       </c>
       <c r="G6">
-        <v>17.59612735644851</v>
+        <v>20.70132630170412</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>35.25388055774796</v>
+      </c>
+      <c r="C7">
         <v>32.79400157853197</v>
-      </c>
-      <c r="C7">
-        <v>35.25388055774796</v>
       </c>
       <c r="D7">
         <v>3.049338146811071</v>
       </c>
       <c r="E7">
-        <v>19.5146771037182</v>
+        <v>20.97847358121331</v>
       </c>
       <c r="F7">
         <v>59.50684931506849</v>
       </c>
       <c r="G7">
-        <v>20.9784735812133</v>
+        <v>19.5146771037182</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.89131622064446</v>
+      </c>
+      <c r="C8">
         <v>37.36755871108684</v>
-      </c>
-      <c r="C8">
-        <v>28.89131622064446</v>
       </c>
       <c r="D8">
         <v>2.676118094124525</v>
       </c>
       <c r="E8">
-        <v>22.47552723211353</v>
+        <v>17.37730766703896</v>
       </c>
       <c r="F8">
         <v>60.14716510084751</v>
       </c>
       <c r="G8">
-        <v>17.37730766703896</v>
+        <v>22.47552723211353</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.97243704144358</v>
+      </c>
+      <c r="C9">
         <v>26.86496133254015</v>
-      </c>
-      <c r="C9">
-        <v>32.97243704144358</v>
       </c>
       <c r="D9">
         <v>3.722320637732507</v>
       </c>
       <c r="E9">
-        <v>16.80768181028708</v>
+        <v>20.62873731484008</v>
       </c>
       <c r="F9">
         <v>62.56358087487283</v>
       </c>
       <c r="G9">
-        <v>20.62873731484008</v>
+        <v>16.80768181028708</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>31.3677145401</v>
+      </c>
+      <c r="C10">
         <v>33.50455448256969</v>
-      </c>
-      <c r="C10">
-        <v>31.3677145401</v>
       </c>
       <c r="D10">
         <v>2.984668847097302</v>
       </c>
       <c r="E10">
-        <v>20.32152203713704</v>
+        <v>19.02546421301874</v>
       </c>
       <c r="F10">
         <v>60.65301374984422</v>
       </c>
       <c r="G10">
-        <v>19.02546421301874</v>
+        <v>20.32152203713704</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.47225840062517</v>
+      </c>
+      <c r="C11">
         <v>41.72961708778328</v>
-      </c>
-      <c r="C11">
-        <v>33.47225840062517</v>
       </c>
       <c r="D11">
         <v>2.396379525593009</v>
       </c>
       <c r="E11">
+        <v>19.10496580434137</v>
+      </c>
+      <c r="F11">
+        <v>57.07701457032412</v>
+      </c>
+      <c r="G11">
         <v>23.81801962533452</v>
-      </c>
-      <c r="F11">
-        <v>57.07701457032411</v>
-      </c>
-      <c r="G11">
-        <v>19.10496580434136</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>30.91570184671323</v>
+      </c>
+      <c r="C12">
         <v>32.96813702038082</v>
-      </c>
-      <c r="C12">
-        <v>30.91570184671323</v>
       </c>
       <c r="D12">
         <v>3.033231751560006</v>
       </c>
       <c r="E12">
-        <v>20.11677127426653</v>
+        <v>18.86439935775799</v>
       </c>
       <c r="F12">
         <v>61.01882936797548</v>
       </c>
       <c r="G12">
-        <v>18.86439935775799</v>
+        <v>20.11677127426653</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>31.95383280534313</v>
+      </c>
+      <c r="C13">
         <v>23.2530922738554</v>
-      </c>
-      <c r="C13">
-        <v>31.95383280534313</v>
       </c>
       <c r="D13">
         <v>4.300503297466157</v>
       </c>
       <c r="E13">
-        <v>14.98199404568442</v>
+        <v>20.58789115823139</v>
       </c>
       <c r="F13">
         <v>64.4301147960842</v>
       </c>
       <c r="G13">
-        <v>20.58789115823139</v>
+        <v>14.98199404568442</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>32.84224841341795</v>
+      </c>
+      <c r="C14">
         <v>30.87035358114234</v>
-      </c>
-      <c r="C14">
-        <v>32.84224841341795</v>
       </c>
       <c r="D14">
         <v>3.23935389133627</v>
       </c>
       <c r="E14">
-        <v>18.8564308459089</v>
+        <v>20.06091651668281</v>
       </c>
       <c r="F14">
         <v>61.08265263740827</v>
       </c>
       <c r="G14">
-        <v>20.06091651668281</v>
+        <v>18.8564308459089</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>30.44982698961938</v>
+      </c>
+      <c r="C15">
         <v>33.78828655645265</v>
-      </c>
-      <c r="C15">
-        <v>30.44982698961938</v>
       </c>
       <c r="D15">
         <v>2.959605537644605</v>
       </c>
       <c r="E15">
-        <v>20.57274394288167</v>
+        <v>18.54004915922126</v>
       </c>
       <c r="F15">
         <v>60.88720689789708</v>
       </c>
       <c r="G15">
-        <v>18.54004915922126</v>
+        <v>20.57274394288167</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>31.78189486368429</v>
+      </c>
+      <c r="C16">
         <v>22.97032685645429</v>
-      </c>
-      <c r="C16">
-        <v>31.78189486368429</v>
       </c>
       <c r="D16">
         <v>4.35344262295082</v>
       </c>
       <c r="E16">
-        <v>14.84329375121666</v>
+        <v>20.53727856725715</v>
       </c>
       <c r="F16">
         <v>64.61942768152618</v>
       </c>
       <c r="G16">
-        <v>20.53727856725715</v>
+        <v>14.84329375121666</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>35.37470886422798</v>
+      </c>
+      <c r="C17">
         <v>38.40252089327305</v>
-      </c>
-      <c r="C17">
-        <v>35.37470886422798</v>
       </c>
       <c r="D17">
         <v>2.603995718872636</v>
       </c>
       <c r="E17">
-        <v>22.09870703248187</v>
+        <v>20.35635446231473</v>
       </c>
       <c r="F17">
         <v>57.5449385052034</v>
       </c>
       <c r="G17">
-        <v>20.35635446231473</v>
+        <v>22.09870703248187</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>32.31288811417365</v>
+      </c>
+      <c r="C18">
         <v>38.32661509968406</v>
-      </c>
-      <c r="C18">
-        <v>32.31288811417365</v>
       </c>
       <c r="D18">
         <v>2.609152927799886</v>
       </c>
       <c r="E18">
-        <v>22.46057587946115</v>
+        <v>18.93634680457128</v>
       </c>
       <c r="F18">
         <v>58.60307731596757</v>
       </c>
       <c r="G18">
-        <v>18.93634680457128</v>
+        <v>22.46057587946115</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>30.02728294013802</v>
+      </c>
+      <c r="C19">
         <v>35.8690418873375</v>
-      </c>
-      <c r="C19">
-        <v>30.02728294013802</v>
       </c>
       <c r="D19">
         <v>2.787919463087248</v>
       </c>
       <c r="E19">
-        <v>21.62136016252298</v>
+        <v>18.10002902195995</v>
       </c>
       <c r="F19">
         <v>60.27861081551708</v>
       </c>
       <c r="G19">
-        <v>18.10002902195995</v>
+        <v>21.62136016252298</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>32.69273618538324</v>
+      </c>
+      <c r="C20">
         <v>27.2894385026738</v>
-      </c>
-      <c r="C20">
-        <v>32.69273618538324</v>
       </c>
       <c r="D20">
         <v>3.664421310471525</v>
       </c>
       <c r="E20">
-        <v>17.05779944289694</v>
+        <v>20.43523676880223</v>
       </c>
       <c r="F20">
         <v>62.50696378830084</v>
       </c>
       <c r="G20">
-        <v>20.43523676880223</v>
+        <v>17.05779944289694</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>32.49019758591528</v>
+      </c>
+      <c r="C21">
         <v>27.46726121831834</v>
-      </c>
-      <c r="C21">
-        <v>32.49019758591528</v>
       </c>
       <c r="D21">
         <v>3.640697891397649</v>
       </c>
       <c r="E21">
-        <v>17.17160388996587</v>
+        <v>20.3117740359197</v>
       </c>
       <c r="F21">
-        <v>62.51662207411442</v>
+        <v>62.51662207411443</v>
       </c>
       <c r="G21">
-        <v>20.3117740359197</v>
+        <v>17.17160388996588</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>37.3489010989011</v>
+      </c>
+      <c r="C22">
         <v>30.59065934065934</v>
-      </c>
-      <c r="C22">
-        <v>37.3489010989011</v>
       </c>
       <c r="D22">
         <v>3.268971710821733</v>
       </c>
       <c r="E22">
-        <v>18.21527891379029</v>
+        <v>22.23948961230165</v>
       </c>
       <c r="F22">
-        <v>59.54523147390807</v>
+        <v>59.54523147390805</v>
       </c>
       <c r="G22">
-        <v>22.23948961230165</v>
+        <v>18.21527891379028</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>31.0782832521963</v>
+      </c>
+      <c r="C23">
         <v>28.77287225113312</v>
-      </c>
-      <c r="C23">
-        <v>31.0782832521963</v>
       </c>
       <c r="D23">
         <v>3.475495915985998</v>
       </c>
       <c r="E23">
-        <v>17.99978996744495</v>
+        <v>19.44201351209438</v>
       </c>
       <c r="F23">
         <v>62.55819652046068</v>
       </c>
       <c r="G23">
-        <v>19.44201351209438</v>
+        <v>17.99978996744495</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>33.19460836076775</v>
+      </c>
+      <c r="C24">
         <v>28.60426113423194</v>
-      </c>
-      <c r="C24">
-        <v>33.19460836076775</v>
       </c>
       <c r="D24">
         <v>3.495982627578719</v>
       </c>
       <c r="E24">
-        <v>17.67890049140049</v>
+        <v>20.51597051597052</v>
       </c>
       <c r="F24">
         <v>61.80512899262899</v>
       </c>
       <c r="G24">
-        <v>20.51597051597052</v>
+        <v>17.67890049140049</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>32.01632350213319</v>
+      </c>
+      <c r="C25">
         <v>38.87961417176776</v>
-      </c>
-      <c r="C25">
-        <v>32.01632350213319</v>
       </c>
       <c r="D25">
         <v>2.572041984732825</v>
       </c>
       <c r="E25">
-        <v>22.75046130467817</v>
+        <v>18.73439704765006</v>
       </c>
       <c r="F25">
         <v>58.51514164767176</v>
       </c>
       <c r="G25">
-        <v>18.73439704765006</v>
+        <v>22.75046130467817</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>39.22745171573223</v>
+      </c>
+      <c r="C26">
         <v>30.7144196512282</v>
-      </c>
-      <c r="C26">
-        <v>39.22745171573223</v>
       </c>
       <c r="D26">
         <v>3.255799755799756</v>
       </c>
       <c r="E26">
-        <v>18.07348560079444</v>
+        <v>23.08286439368862</v>
       </c>
       <c r="F26">
         <v>58.84365000551693</v>
       </c>
       <c r="G26">
-        <v>23.08286439368862</v>
+        <v>18.07348560079444</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>34.51515151515152</v>
+      </c>
+      <c r="C27">
         <v>30.34848484848485</v>
-      </c>
-      <c r="C27">
-        <v>34.51515151515152</v>
       </c>
       <c r="D27">
         <v>3.295057413879181</v>
       </c>
       <c r="E27">
+        <v>20.93557577428545</v>
+      </c>
+      <c r="F27">
+        <v>60.65618968844776</v>
+      </c>
+      <c r="G27">
         <v>18.4082345372668</v>
-      </c>
-      <c r="F27">
-        <v>60.65618968844775</v>
-      </c>
-      <c r="G27">
-        <v>20.93557577428545</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>31.03448275862069</v>
+      </c>
+      <c r="C28">
         <v>36.21816542709038</v>
-      </c>
-      <c r="C28">
-        <v>31.03448275862069</v>
       </c>
       <c r="D28">
         <v>2.761045426260112</v>
       </c>
       <c r="E28">
-        <v>21.65476350896105</v>
+        <v>18.55545074787764</v>
       </c>
       <c r="F28">
         <v>59.7897857431613</v>
       </c>
       <c r="G28">
-        <v>18.55545074787764</v>
+        <v>21.65476350896105</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>32.90712129284319</v>
+      </c>
+      <c r="C29">
         <v>32.40987391227135</v>
-      </c>
-      <c r="C29">
-        <v>32.90712129284319</v>
       </c>
       <c r="D29">
         <v>3.085479452054794</v>
       </c>
       <c r="E29">
-        <v>19.60468363948867</v>
+        <v>19.90546782683424</v>
       </c>
       <c r="F29">
-        <v>60.4898485336771</v>
+        <v>60.48984853367708</v>
       </c>
       <c r="G29">
-        <v>19.90546782683425</v>
+        <v>19.60468363948866</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>32.79066786309448</v>
+      </c>
+      <c r="C30">
         <v>33.36751698500192</v>
-      </c>
-      <c r="C30">
-        <v>32.79066786309448</v>
       </c>
       <c r="D30">
         <v>2.996926623127161</v>
       </c>
       <c r="E30">
-        <v>20.08177750347168</v>
+        <v>19.73460885665792</v>
       </c>
       <c r="F30">
         <v>60.18361363987039</v>
       </c>
       <c r="G30">
-        <v>19.73460885665792</v>
+        <v>20.08177750347168</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>33.04707866891581</v>
+      </c>
+      <c r="C31">
         <v>29.45867198282472</v>
-      </c>
-      <c r="C31">
-        <v>33.04707866891581</v>
       </c>
       <c r="D31">
         <v>3.394586153045289</v>
       </c>
       <c r="E31">
-        <v>18.12777201094649</v>
+        <v>20.33594413513259</v>
       </c>
       <c r="F31">
         <v>61.53628385392092</v>
       </c>
       <c r="G31">
-        <v>20.33594413513259</v>
+        <v>18.12777201094649</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>32.92806484295846</v>
+      </c>
+      <c r="C32">
         <v>36.37284701114488</v>
-      </c>
-      <c r="C32">
-        <v>32.92806484295846</v>
       </c>
       <c r="D32">
         <v>2.749303621169916</v>
       </c>
       <c r="E32">
-        <v>21.48414123279474</v>
+        <v>19.4494314781568</v>
       </c>
       <c r="F32">
         <v>59.06642728904848</v>
       </c>
       <c r="G32">
-        <v>19.4494314781568</v>
+        <v>21.48414123279474</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>29.14747584213854</v>
+      </c>
+      <c r="C33">
         <v>32.46635961347422</v>
-      </c>
-      <c r="C33">
-        <v>29.14747584213854</v>
       </c>
       <c r="D33">
         <v>3.080111265646732</v>
       </c>
       <c r="E33">
-        <v>20.08884915202146</v>
+        <v>18.03526026095946</v>
       </c>
       <c r="F33">
         <v>61.87589058701908</v>
       </c>
       <c r="G33">
-        <v>18.03526026095946</v>
+        <v>20.08884915202146</v>
       </c>
     </row>
   </sheetData>
